--- a/input_data/admin_data/CRI/diverse_CRI_2011.xlsx
+++ b/input_data/admin_data/CRI/diverse_CRI_2011.xlsx
@@ -794,7 +794,7 @@
         <v>0.0049159200862050056</v>
       </c>
       <c r="J29">
-        <v>2.1160659790039062</v>
+        <v>2.1160659790039063</v>
       </c>
     </row>
     <row r="30">

--- a/input_data/admin_data/CRI/diverse_CRI_2011.xlsx
+++ b/input_data/admin_data/CRI/diverse_CRI_2011.xlsx
@@ -794,7 +794,7 @@
         <v>0.0049159200862050056</v>
       </c>
       <c r="J29">
-        <v>2.1160659790039063</v>
+        <v>2.1160659790039062</v>
       </c>
     </row>
     <row r="30">
